--- a/results/ICC空模型.xlsx
+++ b/results/ICC空模型.xlsx
@@ -438,13 +438,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Table X. Null-Model ICC(1) Results for Key Study Variables</t>
+          <t>Null-model ICC(1) results for key Study 3 variables</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -476,17 +476,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>ICC(1)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>Level-1 variance</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>Level-2 variance %</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -498,7 +498,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Thriving</t>
+          <t>Thriving (T3)</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -507,8 +507,10 @@
       <c r="C3" t="n">
         <v>0.87</v>
       </c>
-      <c r="D3" t="n">
-        <v>12.8</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>12.8%</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -519,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OCBS</t>
+          <t>Leader-rated OCBS (T3)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -528,8 +530,10 @@
       <c r="C4" t="n">
         <v>0.79</v>
       </c>
-      <c r="D4" t="n">
-        <v>21.4</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -540,7 +544,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CWBS</t>
+          <t>Leader-rated CWBS (T3)</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -549,8 +553,10 @@
       <c r="C5" t="n">
         <v>0.83</v>
       </c>
-      <c r="D5" t="n">
-        <v>17.1</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>17.1%</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -561,7 +567,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OCBS_Follow</t>
+          <t>Follower-rated OCBS (T3)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -570,8 +576,10 @@
       <c r="C6" t="n">
         <v>0.89</v>
       </c>
-      <c r="D6" t="n">
-        <v>10.8</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>10.8%</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -582,7 +590,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CWBS_Follow</t>
+          <t>Follower-rated CWBS (T3)</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -591,8 +599,10 @@
       <c r="C7" t="n">
         <v>0.86</v>
       </c>
-      <c r="D7" t="n">
-        <v>14.2</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>14.2%</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -603,7 +613,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Benign envy</t>
+          <t>Benign envy (T2)</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -612,8 +622,10 @@
       <c r="C8" t="n">
         <v>0.85</v>
       </c>
-      <c r="D8" t="n">
-        <v>14.8</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>14.8%</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -624,7 +636,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Malicious envy</t>
+          <t>Malicious envy (T2)</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -633,8 +645,10 @@
       <c r="C9" t="n">
         <v>0.87</v>
       </c>
-      <c r="D9" t="n">
-        <v>13.2</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>13.2%</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -645,7 +659,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Note. ICC(1) was calculated...</t>
+          <t>Note. ICC(1) computed from null (empty) random-intercept models. N = 438 followers, J = 79 leaders. ICC(1) ≥ 0.05 suggests non-trivial between-leader variance.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -669,16 +683,11 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Note. ICC(1) was calculated from null (empty) random-intercept models. N = 438 followers, J = 79 leaders.</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12"/>
     <row r="13"/>
     <row r="14"/>
+    <row r="15"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/ICC空模型.xlsx
+++ b/results/ICC空模型.xlsx
@@ -444,29 +444,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Null-model ICC(1) results for key Study 3 variables</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ICC(1)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Level-1 variance</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Level-2 variance %</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 4</t>
-        </is>
-      </c>
+          <t>Table X. Null-Model ICC(1) Results for Key Study Variables</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr"/>
+      <c r="C1" s="1" t="inlineStr"/>
+      <c r="D1" s="1" t="inlineStr"/>
+      <c r="E1" s="1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -491,7 +475,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>NaN</t>
+          <t>Notes</t>
         </is>
       </c>
     </row>
@@ -514,14 +498,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>___</t>
+          <t>Aggregation supported (ICC(1) &gt; 0.05)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Leader-rated OCBS (T3)</t>
+          <t>OCBS (leader-rated, T3)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -537,14 +521,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>___</t>
+          <t>Strong nesting; aggregation supported</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Leader-rated CWBS (T3)</t>
+          <t>CWBS (leader-rated, T3)</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -560,14 +544,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>___</t>
+          <t>Aggregation supported</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Follower-rated OCBS (T3)</t>
+          <t>OCBS (follower-rated, T3)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -583,14 +567,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>___</t>
+          <t>Borderline aggregation; reported for transparency</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Follower-rated CWBS (T3)</t>
+          <t>CWBS (follower-rated, T3)</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -606,7 +590,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>___</t>
+          <t>Aggregation supported</t>
         </is>
       </c>
     </row>
@@ -629,7 +613,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>___</t>
+          <t>Aggregation supported</t>
         </is>
       </c>
     </row>
@@ -652,42 +636,56 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>___</t>
+          <t>Aggregation supported</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Note. ICC(1) computed from null (empty) random-intercept models. N = 438 followers, J = 79 leaders. ICC(1) ≥ 0.05 suggests non-trivial between-leader variance.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
+          <t>Note. ICC(1) computed from null (empty) random-intercept models. N = 360 followers, J = 79 leaders. ICC(1) ≥ 0.05 indicates non-trivial between-leader variance and supports aggregation.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/ICC空模型.xlsx
+++ b/results/ICC空模型.xlsx
@@ -643,7 +643,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Note. ICC(1) computed from null (empty) random-intercept models. N = 360 followers, J = 79 leaders. ICC(1) ≥ 0.05 indicates non-trivial between-leader variance and supports aggregation.</t>
+          <t>Note. ICC(1) computed from null (empty) random-intercept models. N = 362 followers, J = 79 leaders. ICC(1) ≥ 0.05 indicates non-trivial between-leader variance and supports aggregation.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>

--- a/results/ICC空模型.xlsx
+++ b/results/ICC空模型.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,10 +447,26 @@
           <t>Table X. Null-Model ICC(1) Results for Key Study Variables</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr"/>
-      <c r="C1" s="1" t="inlineStr"/>
-      <c r="D1" s="1" t="inlineStr"/>
-      <c r="E1" s="1" t="inlineStr"/>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ICC(1)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Level-1 variance</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Level-2 variance %</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 4</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -460,29 +476,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ICC(1)</t>
+          <t>NaN</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Level-1 variance</t>
+          <t>NaN</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Level-2 variance %</t>
+          <t>NaN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Thriving (T3)</t>
+          <t>Thriving</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -491,21 +507,19 @@
       <c r="C3" t="n">
         <v>0.87</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>12.8%</t>
-        </is>
+      <c r="D3" t="n">
+        <v>12.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aggregation supported (ICC(1) &gt; 0.05)</t>
+          <t>Aggregation supported</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OCBS (leader-rated, T3)</t>
+          <t>OCBS</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -514,21 +528,19 @@
       <c r="C4" t="n">
         <v>0.79</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>21.4%</t>
-        </is>
+      <c r="D4" t="n">
+        <v>21.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Strong nesting; aggregation supported</t>
+          <t>Aggregation supported</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CWBS (leader-rated, T3)</t>
+          <t>CWBS</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -537,10 +549,8 @@
       <c r="C5" t="n">
         <v>0.83</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>17.1%</t>
-        </is>
+      <c r="D5" t="n">
+        <v>17.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -551,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OCBS (follower-rated, T3)</t>
+          <t>OCBS_Follow</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -560,21 +570,19 @@
       <c r="C6" t="n">
         <v>0.89</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>10.8%</t>
-        </is>
+      <c r="D6" t="n">
+        <v>10.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Borderline aggregation; reported for transparency</t>
+          <t>Borderline; reported</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CWBS (follower-rated, T3)</t>
+          <t>CWBS_Follow</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -583,10 +591,8 @@
       <c r="C7" t="n">
         <v>0.86</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>14.2%</t>
-        </is>
+      <c r="D7" t="n">
+        <v>14.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -597,7 +603,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Benign envy (T2)</t>
+          <t>Benign envy</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -606,10 +612,8 @@
       <c r="C8" t="n">
         <v>0.85</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>14.8%</t>
-        </is>
+      <c r="D8" t="n">
+        <v>14.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -620,7 +624,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Malicious envy (T2)</t>
+          <t>Malicious envy</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -629,10 +633,8 @@
       <c r="C9" t="n">
         <v>0.87</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>13.2%</t>
-        </is>
+      <c r="D9" t="n">
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -643,48 +645,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Note. ICC(1) computed from null (empty) random-intercept models. N = 362 followers, J = 79 leaders. ICC(1) ≥ 0.05 indicates non-trivial between-leader variance and supports aggregation.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+          <t>Note. ICC(1) was calculated...</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/results/ICC空模型.xlsx
+++ b/results/ICC空模型.xlsx
@@ -3,45 +3,380 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="14235" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="22">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
       <b val="1"/>
       <color theme="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -51,33 +386,539 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -150,9 +991,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="WPS">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -160,39 +1001,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4874CB"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="EE822F"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="F2BA02"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="75BD42"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="30C0B4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="E54C5E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0026E5"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="7E1FAD"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="WPS">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -224,6 +1065,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -258,177 +1100,140 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="WPS">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumOff val="17500"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:hueOff val="-2520000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:gradFill>
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="phClr">
+                  <a:hueOff val="-4200000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="phClr"/>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="2700000" scaled="1"/>
+          </a:gradFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
+            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:schemeClr val="phClr">
+                <a:alpha val="60000"/>
+              </a:schemeClr>
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
+            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -438,238 +1243,387 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
+  <cols>
+    <col width="24.625" customWidth="1" style="4" min="1" max="1"/>
+    <col width="24.125" customWidth="1" style="4" min="2" max="2"/>
+    <col width="9" customWidth="1" style="4" min="3" max="3"/>
+    <col width="18.25" customWidth="1" style="4" min="4" max="4"/>
+    <col width="20.75" customWidth="1" style="4" min="5" max="5"/>
+    <col width="20.375" customWidth="1" style="4" min="6" max="6"/>
+    <col width="23.875" customWidth="1" style="4" min="7" max="7"/>
+    <col width="9" customWidth="1" style="4" min="8" max="8"/>
+    <col width="17.5" customWidth="1" style="4" min="9" max="9"/>
+    <col width="22.625" customWidth="1" style="4" min="10" max="10"/>
+    <col width="9" customWidth="1" style="4" min="11" max="16384"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="18.75" customHeight="1" s="6">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Table X. Null-Model ICC(1) Results for Key Study Variables</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ICC(1)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Level-1 variance</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Level-2 variance %</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Unnamed: 4</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>NaN</t>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Level-1 unit</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Level-2 unit</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Within variance (σ²)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Between variance (τ00)</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>ICC(1)</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Level-1 variance %</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Level-2 variance %</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Thriving</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Follower-rated</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Follower</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Leader/Team</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G3" s="3" t="n">
         <v>0.13</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="D3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Aggregation supported</t>
-        </is>
+      <c r="H3" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>OCBS</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Leader-rated</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Follower</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Leader/Team</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="D4" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Aggregation supported</t>
-        </is>
+      <c r="H4" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>CWBS</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Leader-rated</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Follower</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Leader/Team</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="G5" s="3" t="n">
         <v>0.17</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="D5" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Aggregation supported</t>
-        </is>
+      <c r="H5" s="3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>OCBS_Follow</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>OCBS</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Follower-rated</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Follower</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Leader/Team</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G6" s="3" t="n">
         <v>0.11</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="D6" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Borderline; reported</t>
-        </is>
+      <c r="H6" s="3" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CWBS_Follow</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>CWBS</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Follower-rated</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Follower</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Leader/Team</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>0.14</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="D7" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Aggregation supported</t>
-        </is>
+      <c r="H7" s="3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Benign envy</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Follower-rated</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Follower</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Leader/Team</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>0.15</v>
       </c>
-      <c r="C8" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="D8" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Aggregation supported</t>
-        </is>
+      <c r="H8" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Malicious envy</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Follower-rated</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Follower</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Leader/Team</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G9" s="3" t="n">
         <v>0.13</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="D9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Aggregation supported</t>
-        </is>
+      <c r="H9" s="3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>13</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Note. ICC(1) was calculated...</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NaN</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>NaN</t>
+    <row r="10" ht="18" customHeight="1" s="6">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Note. ICC(1) was calculated from intercept-only models as τ00 / (τ00 + σ²). Level-2 variance % equals ICC(1) × 100, and Level-1 variance % equals (1 − ICC(1)) × 100.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A10:J10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/ICC空模型.xlsx
+++ b/results/ICC空模型.xlsx
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.87</v>
+        <v>0.547</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.13</v>
+        <v>0.082</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>0.13</v>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.79</v>
+        <v>0.498</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.21</v>
+        <v>0.132</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>0.21</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.83</v>
+        <v>0.519</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.17</v>
+        <v>0.106</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>0.17</v>
@@ -1471,19 +1471,19 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.89</v>
+        <v>0.571</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.11</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>0.11</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>89</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="7">
@@ -1513,10 +1513,10 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.86</v>
+        <v>0.554</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>0.14</v>
@@ -1555,10 +1555,10 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.85</v>
+        <v>0.483</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.15</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0.15</v>
@@ -1597,19 +1597,19 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.87</v>
+        <v>0.532</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.13</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>87</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" s="6">

--- a/results/ICC空模型.xlsx
+++ b/results/ICC空模型.xlsx
@@ -1345,19 +1345,19 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.547</v>
+        <v>0.553</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.082</v>
+        <v>0.075</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>87</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>13</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="4">
@@ -1387,19 +1387,19 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.498</v>
+        <v>0.483</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.132</v>
+        <v>0.179</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.519</v>
+        <v>0.501</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.106</v>
+        <v>0.133</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -1471,19 +1471,19 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.571</v>
+        <v>0.578</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.064</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -1513,19 +1513,19 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.554</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.09</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -1555,19 +1555,19 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0.483</v>
+        <v>0.476</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.091</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -1597,19 +1597,19 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.532</v>
+        <v>0.541</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.08</v>
+        <v>0.067</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>13.1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" s="6">

--- a/results/ICC空模型.xlsx
+++ b/results/ICC空模型.xlsx
@@ -1348,16 +1348,16 @@
         <v>0.553</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0.075</v>
+        <v>0.077</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.12</v>
+        <v>0.122</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>88.09999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="4">
@@ -1390,16 +1390,16 @@
         <v>0.483</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>0.179</v>
+        <v>0.183</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>0.27</v>
+        <v>0.275</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>73</v>
+        <v>72.5</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>27</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="5">
@@ -1432,16 +1432,16 @@
         <v>0.501</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0.133</v>
+        <v>0.137</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>0.21</v>
+        <v>0.215</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>79</v>
+        <v>78.5</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>21</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="6">
@@ -1474,16 +1474,16 @@
         <v>0.578</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.064</v>
+        <v>0.063</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.1</v>
+        <v>0.098</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>90</v>
+        <v>90.2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1516,16 +1516,16 @@
         <v>0.5610000000000001</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.13</v>
+        <v>0.134</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>87</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>13</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="8">
@@ -1558,16 +1558,16 @@
         <v>0.476</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.091</v>
+        <v>0.092</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.16</v>
+        <v>0.162</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>84</v>
+        <v>83.8</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="9">
@@ -1600,16 +1600,16 @@
         <v>0.541</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.067</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.11</v>
+        <v>0.113</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>89</v>
+        <v>88.7</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1" s="6">
